--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。</t>
+    <t>用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。
+**subject 選用規則（回應委員意見）**：**個人健康指導／個案追蹤 → `subject` = Patient**；**群體衛教／全廠宣導 → `subject` = Group**。**事業單位不作為 `subject`**，改以 `extension[employerInfo]` 表達所屬事業單位。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="410">
   <si>
     <t>Property</t>
   </si>
@@ -54,74 +54,77 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2026-07-29T09:46:30+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。
+**subject 選用規則（回應委員意見）**：**個人健康指導／個案追蹤 → `subject` = Patient**；**群體衛教／全廠宣導 → `subject` = Group**。**事業單位不作為 `subject`**，改以 `extension[employerInfo]` 表達所屬事業單位。</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Procedure</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Procedure</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
     <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2026-07-26T18:45:10+08:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。
-**subject 選用規則（回應委員意見）**：**個人健康指導／個案追蹤 → `subject` = Patient**；**群體衛教／全廠宣導 → `subject` = Group**。**事業單位不作為 `subject`**，改以 `extension[employerInfo]` 表達所屬事業單位。</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>resource</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Procedure</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Procedure</t>
-  </si>
-  <si>
-    <t>Abstract</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1582,15 +1585,15 @@
         <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1603,17 +1606,17 @@
   <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.09375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.09375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.7578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.2890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.2890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.77734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1622,148 +1625,148 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.02734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="122.64453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="92.8203125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="122.22265625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="90.15625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
@@ -1779,10 +1782,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>22</v>
@@ -1794,13 +1797,13 @@
         <v>22</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1854,22 +1857,22 @@
         <v>32</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>22</v>
@@ -1880,10 +1883,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1891,10 +1894,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>22</v>
@@ -1903,19 +1906,19 @@
         <v>22</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1965,13 +1968,13 @@
         <v>22</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>22</v>
@@ -1994,10 +1997,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2005,10 +2008,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>22</v>
@@ -2017,16 +2020,16 @@
         <v>22</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2077,19 +2080,19 @@
         <v>22</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>22</v>
@@ -2106,10 +2109,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2117,31 +2120,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2191,19 +2194,19 @@
         <v>22</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>22</v>
@@ -2220,10 +2223,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2231,10 +2234,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>22</v>
@@ -2246,16 +2249,16 @@
         <v>22</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2281,13 +2284,13 @@
         <v>22</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>22</v>
@@ -2305,19 +2308,19 @@
         <v>22</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>22</v>
@@ -2334,21 +2337,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>22</v>
@@ -2360,16 +2363,16 @@
         <v>22</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2419,25 +2422,25 @@
         <v>22</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>22</v>
@@ -2448,21 +2451,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>22</v>
@@ -2474,16 +2477,16 @@
         <v>22</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2533,13 +2536,13 @@
         <v>22</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>22</v>
@@ -2551,7 +2554,7 @@
         <v>22</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>22</v>
@@ -2562,10 +2565,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2573,10 +2576,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>22</v>
@@ -2588,13 +2591,13 @@
         <v>22</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2633,29 +2636,29 @@
         <v>22</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>22</v>
@@ -2672,23 +2675,23 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>22</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>22</v>
@@ -2700,13 +2703,13 @@
         <v>22</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2757,19 +2760,19 @@
         <v>22</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>22</v>
@@ -2786,45 +2789,45 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>22</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>22</v>
@@ -2873,25 +2876,25 @@
         <v>22</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>22</v>
@@ -2902,10 +2905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2913,10 +2916,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>22</v>
@@ -2925,22 +2928,22 @@
         <v>22</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>22</v>
@@ -2989,39 +2992,39 @@
         <v>22</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3029,10 +3032,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>22</v>
@@ -3041,16 +3044,16 @@
         <v>22</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3101,25 +3104,25 @@
         <v>22</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>22</v>
@@ -3130,10 +3133,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3141,10 +3144,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>22</v>
@@ -3153,19 +3156,19 @@
         <v>22</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3215,25 +3218,25 @@
         <v>22</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>22</v>
@@ -3244,21 +3247,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>22</v>
@@ -3267,16 +3270,16 @@
         <v>22</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3327,25 +3330,25 @@
         <v>22</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>22</v>
@@ -3356,21 +3359,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>22</v>
@@ -3379,19 +3382,19 @@
         <v>22</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3441,25 +3444,25 @@
         <v>22</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>22</v>
@@ -3470,10 +3473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3481,31 +3484,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3516,7 +3519,7 @@
         <v>22</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>22</v>
@@ -3531,13 +3534,13 @@
         <v>22</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>22</v>
@@ -3555,28 +3558,28 @@
         <v>22</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>22</v>
@@ -3584,21 +3587,21 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>22</v>
@@ -3607,19 +3610,19 @@
         <v>22</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3645,13 +3648,13 @@
         <v>22</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>22</v>
@@ -3669,25 +3672,25 @@
         <v>22</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>22</v>
@@ -3698,10 +3701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3709,10 +3712,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>22</v>
@@ -3721,16 +3724,16 @@
         <v>22</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3757,13 +3760,13 @@
         <v>22</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>22</v>
@@ -3781,28 +3784,28 @@
         <v>22</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>22</v>
@@ -3810,21 +3813,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>22</v>
@@ -3833,20 +3836,20 @@
         <v>22</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>22</v>
@@ -3871,11 +3874,11 @@
         <v>22</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>22</v>
@@ -3893,50 +3896,50 @@
         <v>22</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>22</v>
@@ -3945,16 +3948,16 @@
         <v>22</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4005,39 +4008,39 @@
         <v>22</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4045,10 +4048,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>22</v>
@@ -4057,19 +4060,19 @@
         <v>22</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4119,39 +4122,39 @@
         <v>22</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4159,10 +4162,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>22</v>
@@ -4171,19 +4174,19 @@
         <v>22</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4233,39 +4236,39 @@
         <v>22</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4273,10 +4276,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>22</v>
@@ -4285,16 +4288,16 @@
         <v>22</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4345,28 +4348,28 @@
         <v>22</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>22</v>
@@ -4374,10 +4377,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4385,10 +4388,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>22</v>
@@ -4397,16 +4400,16 @@
         <v>22</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4457,28 +4460,28 @@
         <v>22</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>22</v>
@@ -4486,10 +4489,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4497,10 +4500,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>22</v>
@@ -4509,16 +4512,16 @@
         <v>22</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4569,25 +4572,25 @@
         <v>22</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>22</v>
@@ -4598,10 +4601,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4609,10 +4612,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>22</v>
@@ -4624,13 +4627,13 @@
         <v>22</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4681,13 +4684,13 @@
         <v>22</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>22</v>
@@ -4699,7 +4702,7 @@
         <v>22</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>22</v>
@@ -4710,21 +4713,21 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>22</v>
@@ -4736,16 +4739,16 @@
         <v>22</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4795,25 +4798,25 @@
         <v>22</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>22</v>
@@ -4824,45 +4827,45 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>22</v>
@@ -4911,25 +4914,25 @@
         <v>22</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>22</v>
@@ -4940,10 +4943,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4951,10 +4954,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>22</v>
@@ -4963,20 +4966,20 @@
         <v>22</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>22</v>
@@ -5001,13 +5004,13 @@
         <v>22</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>22</v>
@@ -5025,39 +5028,39 @@
         <v>22</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5065,10 +5068,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>22</v>
@@ -5077,20 +5080,20 @@
         <v>22</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>22</v>
@@ -5139,39 +5142,39 @@
         <v>22</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5179,10 +5182,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>22</v>
@@ -5194,17 +5197,17 @@
         <v>22</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>22</v>
@@ -5253,25 +5256,25 @@
         <v>22</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>22</v>
@@ -5282,10 +5285,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5293,10 +5296,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>22</v>
@@ -5305,20 +5308,20 @@
         <v>22</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>22</v>
@@ -5367,28 +5370,28 @@
         <v>22</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>22</v>
@@ -5396,10 +5399,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5407,10 +5410,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>22</v>
@@ -5419,19 +5422,19 @@
         <v>22</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5457,13 +5460,13 @@
         <v>22</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>22</v>
@@ -5481,28 +5484,28 @@
         <v>22</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>22</v>
@@ -5510,10 +5513,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5521,10 +5524,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>22</v>
@@ -5533,19 +5536,19 @@
         <v>22</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5595,28 +5598,28 @@
         <v>22</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>22</v>
@@ -5624,10 +5627,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5635,10 +5638,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>22</v>
@@ -5647,19 +5650,19 @@
         <v>22</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5685,13 +5688,13 @@
         <v>22</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>22</v>
@@ -5709,39 +5712,39 @@
         <v>22</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5749,10 +5752,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>22</v>
@@ -5761,19 +5764,19 @@
         <v>22</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5799,13 +5802,13 @@
         <v>22</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>22</v>
@@ -5823,25 +5826,25 @@
         <v>22</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>22</v>
@@ -5852,10 +5855,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5863,10 +5866,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>22</v>
@@ -5878,16 +5881,16 @@
         <v>22</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5937,25 +5940,25 @@
         <v>22</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>22</v>
@@ -5966,10 +5969,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5977,10 +5980,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>22</v>
@@ -5992,16 +5995,16 @@
         <v>22</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6027,13 +6030,13 @@
         <v>22</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>22</v>
@@ -6051,25 +6054,25 @@
         <v>22</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>22</v>
@@ -6080,10 +6083,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6091,10 +6094,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>22</v>
@@ -6106,17 +6109,17 @@
         <v>22</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>22</v>
@@ -6165,25 +6168,25 @@
         <v>22</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>22</v>
@@ -6194,10 +6197,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6205,10 +6208,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>22</v>
@@ -6220,13 +6223,13 @@
         <v>22</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6253,13 +6256,13 @@
         <v>22</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>22</v>
@@ -6277,25 +6280,25 @@
         <v>22</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>22</v>
@@ -6306,10 +6309,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6317,10 +6320,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>22</v>
@@ -6332,13 +6335,13 @@
         <v>22</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6389,39 +6392,39 @@
         <v>22</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6429,10 +6432,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>22</v>
@@ -6444,13 +6447,13 @@
         <v>22</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6501,25 +6504,25 @@
         <v>22</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>22</v>
@@ -6530,10 +6533,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6541,10 +6544,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>22</v>
@@ -6556,13 +6559,13 @@
         <v>22</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6613,13 +6616,13 @@
         <v>22</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>22</v>
@@ -6631,7 +6634,7 @@
         <v>22</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>22</v>
@@ -6642,21 +6645,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>22</v>
@@ -6668,16 +6671,16 @@
         <v>22</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6727,25 +6730,25 @@
         <v>22</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>22</v>
@@ -6756,45 +6759,45 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>22</v>
@@ -6843,25 +6846,25 @@
         <v>22</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>22</v>
@@ -6872,10 +6875,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6883,10 +6886,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>22</v>
@@ -6898,13 +6901,13 @@
         <v>22</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6931,13 +6934,13 @@
         <v>22</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>22</v>
@@ -6955,25 +6958,25 @@
         <v>22</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>22</v>
@@ -6984,10 +6987,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6995,10 +6998,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>22</v>
@@ -7010,13 +7013,13 @@
         <v>22</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7067,25 +7070,25 @@
         <v>22</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>22</v>
@@ -7096,10 +7099,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7107,10 +7110,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>22</v>
@@ -7122,19 +7125,19 @@
         <v>22</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>22</v>
@@ -7183,25 +7186,25 @@
         <v>22</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>22</v>
@@ -7212,10 +7215,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7223,10 +7226,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>22</v>
@@ -7238,16 +7241,16 @@
         <v>22</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7273,13 +7276,13 @@
         <v>22</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>22</v>
@@ -7297,25 +7300,25 @@
         <v>22</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。
+    <t>【依據：勞工健康保護規則附表】用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。
 **subject 選用規則（回應委員意見）**：**個人健康指導／個案追蹤 → `subject` = Patient**；**群體衛教／全廠宣導 → `subject` = Group**。**事業單位不作為 `subject`**，改以 `extension[employerInfo]` 表達所屬事業單位。</t>
   </si>
   <si>
@@ -463,7 +463,7 @@
     <t>雇主事業單位資訊擴充</t>
   </si>
   <si>
-    <t>關聯受檢勞工所屬之事業單位組織資料，或臨場服務事件/活動所針對之事業單位。</t>
+    <t>【技術規格】關聯受檢勞工所屬之事業單位組織資料，或臨場服務事件/活動所針對之事業單位。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,8 @@
   </si>
   <si>
     <t>【依據：勞工健康保護規則附表】用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。
+* ^status = #draft
+* ^extension[http://hl7.org/fhir/StructureDefinition/structuredefinition-standards-status].valueCode = #draft
 **subject 選用規則（回應委員意見）**：**個人健康指導／個案追蹤 → `subject` = Patient**；**群體衛教／全廠宣導 → `subject` = Group**。**事業單位不作為 `subject`**，改以 `extension[employerInfo]` 表達所屬事業單位。</t>
   </si>
   <si>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,8 +88,6 @@
   </si>
   <si>
     <t>【依據：勞工健康保護規則附表】用於記錄醫護人員在臨場健康服務中實際辦理之活動項目（對應附表八之臨場健康服務執行情形），繼承自 TW Core Procedure。
-* ^status = #draft
-* ^extension[http://hl7.org/fhir/StructureDefinition/structuredefinition-standards-status].valueCode = #draft
 **subject 選用規則（回應委員意見）**：**個人健康指導／個案追蹤 → `subject` = Patient**；**群體衛教／全廠宣導 → `subject` = Group**。**事業單位不作為 `subject`**，改以 `extension[employerInfo]` 表達所屬事業單位。</t>
   </si>
   <si>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
+++ b/StructureDefinition-TWHA-Procedure-ServiceActivity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
